--- a/projects/fee_matrix_engine/data/matrix_spec_visual.xlsx
+++ b/projects/fee_matrix_engine/data/matrix_spec_visual.xlsx
@@ -6,7 +6,7 @@
   <sheets>
     <sheet sheetId="1" name="全条件マトリックス" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="基本料金サマリー" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="係数・フラグ制約" state="visible" r:id="rId6"/>
+    <sheet sheetId="3" name="係数・フラグ if-case 分岐" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="算出フロー" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
@@ -35,27 +35,26 @@
   </si>
   <si>
     <t xml:space="preserve">基本料金: ¥80,000
-─── 条件分岐 ───
-  優先度上限 ×1.50
-  環境評価フラグ: 不可
-  共同申請フラグ: 不可
-  リピーター割引 上限15%
+── if/case 分岐ルール ──
+  if 優先度係数 &gt; ×1.50 → case: ×1.50 に差替
+  if 環境評価フラグON → case: 不適用（このセルは使用不可）
+  if 共同申請フラグON → case: 不適用（このセルは使用不可）
+  if リピーター割引率 &gt; 15% → case: 15% に差替
   ※ 一般建設業のみ</t>
   </si>
   <si>
     <t xml:space="preserve">基本料金: ¥150,000
-＋¥20,000 [法人登記確認料]
-─── 条件分岐 ───
-  ＋¥20,000 法人登記確認料
+── if/case 分岐ルール ──
+  if 本セル → +¥20,000加算 [法人登記確認料]
   ※ 特定建設業対応</t>
   </si>
   <si>
     <t xml:space="preserve">基本料金: ¥60,000
-─── 条件分岐 ───
-  優先度上限 ×1.50
-  複雑度上限 ×1.45
-  共同申請フラグ: 不可
-  パッケージ割引 上限15%
+── if/case 分岐ルール ──
+  if 優先度係数 &gt; ×1.50 → case: ×1.50 に差替
+  if 複雑度係数 &gt; ×1.45 → case: ×1.45 に差替
+  if 共同申請フラグON → case: 不適用（このセルは使用不可）
+  if パッケージ割引率 &gt; 15% → case: 15% に差替
   ※ 予算決裁で最急不可</t>
   </si>
   <si>
@@ -63,28 +62,27 @@
   </si>
   <si>
     <t xml:space="preserve">基本料金: ¥50,000
-─── 条件分岐 ───
-  優先度上限 ×1.50
-  環境評価フラグ: 不可
-  共同申請フラグ: 不可
-  リピーター割引 上限15%</t>
+── if/case 分岐ルール ──
+  if 優先度係数 &gt; ×1.50 → case: ×1.50 に差替
+  if 環境評価フラグON → case: 不適用（このセルは使用不可）
+  if 共同申請フラグON → case: 不適用（このセルは使用不可）
+  if リピーター割引率 &gt; 15% → case: 15% に差替</t>
   </si>
   <si>
     <t xml:space="preserve">基本料金: ¥90,000
-＋¥10,000 [法人営業実態確認料]
-─── 条件分岐 ───
-  ＋¥10,000 法人営業実態確認料
+── if/case 分岐ルール ──
+  if 本セル → +¥10,000加算 [法人営業実態確認料]
   ※ 複数店舗・FC対応</t>
   </si>
   <si>
     <t xml:space="preserve">基本料金: ¥40,000
-─── 条件分岐 ───
-  優先度上限 ×1.00
-  複雑度上限 ×1.00
-  環境評価フラグ: 不可
-  共同申請フラグ: 不可
-  翻訳フラグ: 不可
-  パッケージ割引 上限10%
+── if/case 分岐ルール ──
+  if 優先度係数 &gt; ×1.00 → case: ×1.00 に差替
+  if 複雑度係数 &gt; ×1.00 → case: ×1.00 に差替
+  if 環境評価フラグON → case: 不適用（このセルは使用不可）
+  if 共同申請フラグON → case: 不適用（このセルは使用不可）
+  if 翻訳フラグON → case: 不適用（このセルは使用不可）
+  if パッケージ割引率 &gt; 10% → case: 10% に差替
   ※ 定型フォーマット（係数全て1.0）</t>
   </si>
   <si>
@@ -92,26 +90,25 @@
   </si>
   <si>
     <t xml:space="preserve">基本料金: ¥30,000
-─── 条件分岐 ───
-  優先度上限 ×1.50
-  環境評価フラグ: 不可
-  共同申請フラグ: 不可
-  リピーター割引 上限10%</t>
+── if/case 分岐ルール ──
+  if 優先度係数 &gt; ×1.50 → case: ×1.50 に差替
+  if 環境評価フラグON → case: 不適用（このセルは使用不可）
+  if 共同申請フラグON → case: 不適用（このセルは使用不可）
+  if リピーター割引率 &gt; 10% → case: 10% に差替</t>
   </si>
   <si>
     <t xml:space="preserve">基本料金: ¥60,000
-＋¥15,000 [事業計画書作成支援料]
-─── 条件分岐 ───
-  ＋¥15,000 事業計画書作成支援料</t>
+── if/case 分岐ルール ──
+  if 本セル → +¥15,000加算 [事業計画書作成支援料]</t>
   </si>
   <si>
     <t xml:space="preserve">基本料金: ¥20,000
-─── 条件分岐 ───
-  優先度上限 ×1.00
-  複雑度上限 ×1.00
-  環境評価フラグ: 不可
-  共同申請フラグ: 不可
-  翻訳フラグ: 不可
+── if/case 分岐ルール ──
+  if 優先度係数 &gt; ×1.00 → case: ×1.00 に差替
+  if 複雑度係数 &gt; ×1.00 → case: ×1.00 に差替
+  if 環境評価フラグON → case: 不適用（このセルは使用不可）
+  if 共同申請フラグON → case: 不適用（このセルは使用不可）
+  if 翻訳フラグON → case: 不適用（このセルは使用不可）
   ※ 定型フォーマット</t>
   </si>
   <si>
@@ -119,102 +116,96 @@
   </si>
   <si>
     <t xml:space="preserve">基本料金: ¥70,000
-＋¥10,000 [個人通関コンサル料]
-─── 条件分岐 ───
-  ＋¥10,000 個人通関コンサル料
-  優先度上限 ×1.50
-  環境評価フラグ: 不可
-  共同申請フラグ: 不可
-  リピーター割引 上限15%</t>
+── if/case 分岐ルール ──
+  if 本セル → +¥10,000加算 [個人通関コンサル料]
+  if 優先度係数 &gt; ×1.50 → case: ×1.50 に差替
+  if 環境評価フラグON → case: 不適用（このセルは使用不可）
+  if 共同申請フラグON → case: 不適用（このセルは使用不可）
+  if リピーター割引率 &gt; 15% → case: 15% に差替</t>
   </si>
   <si>
     <t xml:space="preserve">基本料金: ¥130,000
-＋¥30,000 [通関業者連携調整料]
-─── 条件分岐 ───
-  ＋¥30,000 通関業者連携調整料</t>
+── if/case 分岐ルール ──
+  if 本セル → +¥30,000加算 [通関業者連携調整料]</t>
   </si>
   <si>
     <t xml:space="preserve">基本料金: ¥50,000
-─── 条件分岐 ───
-  優先度上限 ×1.50
-  複雑度上限 ×1.45
-  共同申請フラグ: 不可
-  パッケージ割引 上限15%</t>
+── if/case 分岐ルール ──
+  if 優先度係数 &gt; ×1.50 → case: ×1.50 に差替
+  if 複雑度係数 &gt; ×1.45 → case: ×1.45 に差替
+  if 共同申請フラグON → case: 不適用（このセルは使用不可）
+  if パッケージ割引率 &gt; 15% → case: 15% に差替</t>
   </si>
   <si>
     <t>E: 宅建免許</t>
   </si>
   <si>
     <t xml:space="preserve">基本料金: ¥100,000
-─── 条件分岐 ───
-  優先度上限 ×1.50
-  環境評価フラグ: 不可
-  共同申請フラグ: 不可
-  リピーター割引 上限15%</t>
+── if/case 分岐ルール ──
+  if 優先度係数 &gt; ×1.50 → case: ×1.50 に差替
+  if 環境評価フラグON → case: 不適用（このセルは使用不可）
+  if 共同申請フラグON → case: 不適用（このセルは使用不可）
+  if リピーター割引率 &gt; 15% → case: 15% に差替</t>
   </si>
   <si>
     <t xml:space="preserve">基本料金: ¥180,000
-＋¥25,000 [事務所実地確認料]
-─── 条件分岐 ───
-  ＋¥25,000 事務所実地確認料</t>
+── if/case 分岐ルール ──
+  if 本セル → +¥25,000加算 [事務所実地確認料]</t>
   </si>
   <si>
     <t xml:space="preserve">基本料金: ¥70,000
-─── 条件分岐 ───
-  優先度上限 ×1.50
-  複雑度上限 ×1.45
-  環境評価フラグ: 不可
-  共同申請フラグ: 不可
-  パッケージ割引 上限15%</t>
+── if/case 分岐ルール ──
+  if 優先度係数 &gt; ×1.50 → case: ×1.50 に差替
+  if 複雑度係数 &gt; ×1.45 → case: ×1.45 に差替
+  if 環境評価フラグON → case: 不適用（このセルは使用不可）
+  if 共同申請フラグON → case: 不適用（このセルは使用不可）
+  if パッケージ割引率 &gt; 15% → case: 15% に差替</t>
   </si>
   <si>
     <t>F: 産廃許可</t>
   </si>
   <si>
     <t xml:space="preserve">基本料金: ¥120,000
-＋¥15,000 [現地施設確認料]
-─── 条件分岐 ───
-  ＋¥15,000 現地施設確認料
-  優先度上限 ×1.50
-  共同申請フラグ: 不可
-  リピーター割引 上限15%</t>
+── if/case 分岐ルール ──
+  if 本セル → +¥15,000加算 [現地施設確認料]
+  if 優先度係数 &gt; ×1.50 → case: ×1.50 に差替
+  if 共同申請フラグON → case: 不適用（このセルは使用不可）
+  if リピーター割引率 &gt; 15% → case: 15% に差替</t>
   </si>
   <si>
     <t xml:space="preserve">基本料金: ¥220,000
-＋¥35,000 [現地施設確認料]
-─── 条件分岐 ───
-  ＋¥35,000 現地施設確認料</t>
+── if/case 分岐ルール ──
+  if 本セル → +¥35,000加算 [現地施設確認料]</t>
   </si>
   <si>
     <t xml:space="preserve">基本料金: ¥80,000
-＋¥10,000 [行政施設確認料]
-─── 条件分岐 ───
-  ＋¥10,000 行政施設確認料
-  優先度上限 ×1.50
-  複雑度上限 ×1.45
-  共同申請フラグ: 不可
-  パッケージ割引 上限15%</t>
+── if/case 分岐ルール ──
+  if 本セル → +¥10,000加算 [行政施設確認料]
+  if 優先度係数 &gt; ×1.50 → case: ×1.50 に差替
+  if 複雑度係数 &gt; ×1.45 → case: ×1.45 に差替
+  if 共同申請フラグON → case: 不適用（このセルは使用不可）
+  if パッケージ割引率 &gt; 15% → case: 15% に差替</t>
   </si>
   <si>
     <t xml:space="preserve">　</t>
   </si>
   <si>
-    <t>標準（追加料金なし・制約なし）</t>
+    <t>分岐なし（全条件がデフォルト値）</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>セル固有追加料金あり（制約なし）</t>
-  </si>
-  <si>
-    <t>制約あり（一部フラグ不可 / 割引上限あり）</t>
-  </si>
-  <si>
-    <t>追加料金あり ＋ 制約あり</t>
-  </si>
-  <si>
-    <t>強制約: 係数が1.0に固定（最急・超複雑が効かない）</t>
+    <t>if 本セル → 固有追加料金を加算する分岐あり</t>
+  </si>
+  <si>
+    <t>if 条件値 &gt; 閾値 → caseで値を差替える分岐あり</t>
+  </si>
+  <si>
+    <t>追加料金加算 ＋ case差替え、複数の分岐あり</t>
+  </si>
+  <si>
+    <t>全係数が if 入力値 → case: 1.0 固定（最急・超複雑も無効化）</t>
   </si>
   <si>
     <t>申請種別</t>
@@ -281,42 +272,53 @@
   </si>
   <si>
     <t xml:space="preserve">優先度
-上限</t>
+if/case</t>
   </si>
   <si>
     <t xml:space="preserve">複雑度
-上限</t>
-  </si>
-  <si>
-    <t xml:space="preserve">制約フラグ
+if/case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">フラグ分岐
 (環境/共同/翻訳)</t>
   </si>
   <si>
-    <t>×1.50</t>
-  </si>
-  <si>
-    <t>×2.10</t>
-  </si>
-  <si>
-    <t>✗環 / ✗共 / ✓翻</t>
-  </si>
-  <si>
-    <t>×2.20</t>
-  </si>
-  <si>
-    <t>✓環 / ✓共 / ✓翻</t>
-  </si>
-  <si>
-    <t>×1.45</t>
-  </si>
-  <si>
-    <t>✓環 / ✗共 / ✓翻</t>
-  </si>
-  <si>
-    <t>×1.00</t>
-  </si>
-  <si>
-    <t>✗環 / ✗共 / ✗翻</t>
+    <t xml:space="preserve">if &gt; ×1.50 →
+case: ×1.50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">×2.10
+(分岐なし)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if 環境ON →
+  case: 不適用 / if 共同ON →
+  case: 不適用 / 翻訳: スルー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">×2.20
+(分岐なし)</t>
+  </si>
+  <si>
+    <t>環境: スルー / 共同: スルー / 翻訳: スルー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if &gt; ×1.45 →
+case: ×1.45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">環境: スルー / if 共同ON →
+  case: 不適用 / 翻訳: スルー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if 入力値 →
+case: ×1.00 固定</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if 環境ON →
+  case: 不適用 / if 共同ON →
+  case: 不適用 / if 翻訳ON →
+  case: 不適用</t>
   </si>
   <si>
     <t>料金算出パイプライン — Step ごとの分岐ポイント</t>
